--- a/samples/clover/design-data/xlsx/Consumables.xlsx
+++ b/samples/clover/design-data/xlsx/Consumables.xlsx
@@ -14,16 +14,16 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1"><![CDATA[Tarot!$B$2:$D$26]]></definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1"><![CDATA[TarotEffect!$B$2:$BL$26]]></definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1"><![CDATA[TarotEffect!$B$2:$BM$26]]></definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1"><![CDATA[Planet!$B$2:$E$16]]></definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1"><![CDATA[Spectral!$B$2:$D$22]]></definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1"><![CDATA[SpectralEffect!$B$2:$BL$31]]></definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1"><![CDATA[SpectralEffect!$B$2:$BM$31]]></definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="931" uniqueCount="297">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="933" uniqueCount="298">
   <si>
     <t xml:space="preserve">:table Tarot(key=tarot_id)</t>
   </si>
@@ -392,6 +392,9 @@
   </si>
   <si>
     <t xml:space="preserve">operation.handler</t>
+  </si>
+  <si>
+    <t xml:space="preserve">operation.sticker</t>
   </si>
   <si>
     <t xml:space="preserve">foreign Tarot</t>
@@ -1423,7 +1426,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:BL26"/>
+  <dimension ref="A1:BM26"/>
   <sheetFormatPr defaultColWidth="8.43" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="45.703125" customWidth="1"/>
@@ -1473,7 +1476,7 @@
     <col min="59" max="60" width="23.4375" customWidth="1"/>
     <col min="61" max="61" width="18.75" customWidth="1"/>
     <col min="62" max="63" width="21.09375" customWidth="1"/>
-    <col min="64" max="64" width="22.265625" customWidth="1"/>
+    <col min="64" max="65" width="22.265625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1545,6 +1548,7 @@
       <c r="BJ1" s="2"/>
       <c r="BK1" s="2"/>
       <c r="BL1" s="2"/>
+      <c r="BM1" s="2"/>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
@@ -1739,43 +1743,46 @@
       <c r="BL2" s="4" t="s">
         <v>122</v>
       </c>
+      <c r="BM2" s="4" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="G3" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="K3" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="H3" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="J3" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="K3" s="4" t="s">
-        <v>126</v>
-      </c>
       <c r="L3" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="M3" s="4"/>
       <c r="N3" s="4"/>
@@ -1792,7 +1799,7 @@
       <c r="Y3" s="4"/>
       <c r="Z3" s="4"/>
       <c r="AA3" s="4" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="AB3" s="4"/>
       <c r="AC3" s="4"/>
@@ -1831,43 +1838,44 @@
       <c r="BJ3" s="4"/>
       <c r="BK3" s="4"/>
       <c r="BL3" s="4"/>
+      <c r="BM3" s="4"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
         <v>10</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="L4" s="4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="M4" s="4"/>
       <c r="N4" s="4"/>
@@ -1884,7 +1892,7 @@
       <c r="Y4" s="4"/>
       <c r="Z4" s="4"/>
       <c r="AA4" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AB4" s="4"/>
       <c r="AC4" s="4"/>
@@ -1923,6 +1931,7 @@
       <c r="BJ4" s="4"/>
       <c r="BK4" s="4"/>
       <c r="BL4" s="4"/>
+      <c r="BM4" s="4"/>
     </row>
     <row r="5">
       <c r="B5" s="5" t="s">
@@ -1932,37 +1941,37 @@
         <v>0</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L5" s="5" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AA5" s="5" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="AT5" s="5" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AU5" s="5">
         <v>1</v>
@@ -1976,40 +1985,40 @@
         <v>0</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="K6" s="6">
         <v>2</v>
       </c>
       <c r="L6" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AA6" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AY6" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="BB6" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="7">
@@ -2020,43 +2029,43 @@
         <v>0</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="K7" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L7" s="5" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AA7" s="5" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="AT7" s="5" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AU7" s="5">
         <v>2</v>
       </c>
       <c r="BJ7" s="5" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="8">
@@ -2067,40 +2076,40 @@
         <v>0</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="K8" s="6">
         <v>2</v>
       </c>
       <c r="L8" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AA8" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AY8" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="BB8" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="9">
@@ -2111,43 +2120,43 @@
         <v>0</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="K9" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L9" s="5" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AA9" s="5" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="AT9" s="5" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AU9" s="5">
         <v>2</v>
       </c>
       <c r="BJ9" s="5" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="10">
@@ -2158,40 +2167,40 @@
         <v>0</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="K10" s="6">
         <v>2</v>
       </c>
       <c r="L10" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AA10" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AY10" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="BB10" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="11">
@@ -2202,40 +2211,40 @@
         <v>0</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="K11" s="5">
         <v>1</v>
       </c>
       <c r="L11" s="5" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AA11" s="5" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AY11" s="5" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="BB11" s="5" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="12">
@@ -2246,40 +2255,40 @@
         <v>0</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="K12" s="6">
         <v>1</v>
       </c>
       <c r="L12" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AA12" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AY12" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="BB12" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="13">
@@ -2290,40 +2299,40 @@
         <v>0</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="K13" s="5">
         <v>1</v>
       </c>
       <c r="L13" s="5" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AA13" s="5" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AY13" s="5" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="BB13" s="5" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="14">
@@ -2334,34 +2343,34 @@
         <v>0</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="K14" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L14" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AA14" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AE14" s="6">
         <v>20</v>
@@ -2378,7 +2387,7 @@
         <v>0</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E15" s="5">
         <v>1</v>
@@ -2387,28 +2396,28 @@
         <v>4</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J15" s="5" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="K15" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L15" s="5" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AA15" s="5" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="BJ15" s="5" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="16">
@@ -2419,40 +2428,40 @@
         <v>0</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J16" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="K16" s="6">
         <v>2</v>
       </c>
       <c r="L16" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AA16" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AH16" s="6">
         <v>1</v>
       </c>
       <c r="BB16" s="6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="17">
@@ -2463,34 +2472,34 @@
         <v>0</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J17" s="5" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="K17" s="5">
         <v>2</v>
       </c>
       <c r="L17" s="5" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AA17" s="5" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AU17" s="5">
         <v>2</v>
@@ -2504,37 +2513,37 @@
         <v>0</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J18" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="K18" s="6">
         <v>2</v>
       </c>
       <c r="L18" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AA18" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="BB18" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="19">
@@ -2545,43 +2554,43 @@
         <v>0</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I19" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J19" s="5" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="K19" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L19" s="5" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AA19" s="5" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AE19" s="5">
         <v>50</v>
       </c>
       <c r="AF19" s="5" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AG19" s="5" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AH19" s="5">
         <v>1</v>
@@ -2595,40 +2604,40 @@
         <v>0</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J20" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="K20" s="6">
         <v>1</v>
       </c>
       <c r="L20" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AA20" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AY20" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="BB20" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="21">
@@ -2639,40 +2648,40 @@
         <v>0</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I21" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J21" s="5" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="K21" s="5">
         <v>1</v>
       </c>
       <c r="L21" s="5" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AA21" s="5" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AY21" s="5" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="BB21" s="5" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="22">
@@ -2683,40 +2692,40 @@
         <v>0</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I22" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J22" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="K22" s="6">
         <v>3</v>
       </c>
       <c r="L22" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AA22" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="BA22" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="BB22" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="23">
@@ -2727,40 +2736,40 @@
         <v>0</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I23" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J23" s="5" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="K23" s="5">
         <v>3</v>
       </c>
       <c r="L23" s="5" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AA23" s="5" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="BA23" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="BB23" s="5" t="s">
         <v>176</v>
-      </c>
-      <c r="BB23" s="5" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="24">
@@ -2771,40 +2780,40 @@
         <v>0</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I24" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J24" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="K24" s="6">
         <v>3</v>
       </c>
       <c r="L24" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AA24" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="BA24" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="BB24" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="25">
@@ -2815,43 +2824,43 @@
         <v>0</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I25" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J25" s="5" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="K25" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L25" s="5" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AA25" s="5" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="AT25" s="5" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AU25" s="5">
         <v>1</v>
       </c>
       <c r="BJ25" s="5" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="26">
@@ -2862,44 +2871,44 @@
         <v>0</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I26" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J26" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="K26" s="6">
         <v>3</v>
       </c>
       <c r="L26" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AA26" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="BA26" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="BB26" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B2:BL26"/>
+  <autoFilter ref="B2:BM26"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2918,10 +2927,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
@@ -2932,13 +2941,13 @@
         <v>2</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>4</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E2" s="4" t="s">
         <v>5</v>
@@ -2952,13 +2961,13 @@
         <v>7</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="4">
@@ -2972,7 +2981,7 @@
         <v>12</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>13</v>
@@ -2980,13 +2989,13 @@
     </row>
     <row r="5">
       <c r="B5" s="5" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E5" s="5">
         <v>1</v>
@@ -2994,13 +3003,13 @@
     </row>
     <row r="6">
       <c r="B6" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E6" s="6">
         <v>2</v>
@@ -3008,13 +3017,13 @@
     </row>
     <row r="7">
       <c r="B7" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E7" s="5">
         <v>3</v>
@@ -3022,13 +3031,13 @@
     </row>
     <row r="8">
       <c r="B8" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E8" s="6">
         <v>4</v>
@@ -3036,13 +3045,13 @@
     </row>
     <row r="9">
       <c r="B9" s="5" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E9" s="5">
         <v>5</v>
@@ -3050,13 +3059,13 @@
     </row>
     <row r="10">
       <c r="B10" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E10" s="6">
         <v>6</v>
@@ -3064,13 +3073,13 @@
     </row>
     <row r="11">
       <c r="B11" s="5" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E11" s="5">
         <v>7</v>
@@ -3078,13 +3087,13 @@
     </row>
     <row r="12">
       <c r="B12" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E12" s="6">
         <v>8</v>
@@ -3092,13 +3101,13 @@
     </row>
     <row r="13">
       <c r="B13" s="5" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E13" s="5">
         <v>9</v>
@@ -3106,13 +3115,13 @@
     </row>
     <row r="14">
       <c r="B14" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E14" s="6">
         <v>10</v>
@@ -3120,13 +3129,13 @@
     </row>
     <row r="15">
       <c r="B15" s="5" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E15" s="5">
         <v>11</v>
@@ -3134,13 +3143,13 @@
     </row>
     <row r="16">
       <c r="B16" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E16" s="6">
         <v>12</v>
@@ -3165,10 +3174,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
@@ -3178,7 +3187,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>4</v>
@@ -3195,10 +3204,10 @@
         <v>7</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="4">
@@ -3217,10 +3226,10 @@
     </row>
     <row r="5">
       <c r="B5" s="5" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D5" s="5">
         <v>1</v>
@@ -3228,10 +3237,10 @@
     </row>
     <row r="6">
       <c r="B6" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D6" s="6">
         <v>2</v>
@@ -3239,10 +3248,10 @@
     </row>
     <row r="7">
       <c r="B7" s="5" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D7" s="5">
         <v>3</v>
@@ -3250,10 +3259,10 @@
     </row>
     <row r="8">
       <c r="B8" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D8" s="6">
         <v>4</v>
@@ -3261,10 +3270,10 @@
     </row>
     <row r="9">
       <c r="B9" s="5" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D9" s="5">
         <v>5</v>
@@ -3272,10 +3281,10 @@
     </row>
     <row r="10">
       <c r="B10" s="6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D10" s="6">
         <v>6</v>
@@ -3283,10 +3292,10 @@
     </row>
     <row r="11">
       <c r="B11" s="5" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D11" s="5">
         <v>7</v>
@@ -3294,10 +3303,10 @@
     </row>
     <row r="12">
       <c r="B12" s="6" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D12" s="6">
         <v>8</v>
@@ -3305,10 +3314,10 @@
     </row>
     <row r="13">
       <c r="B13" s="5" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D13" s="5">
         <v>9</v>
@@ -3316,10 +3325,10 @@
     </row>
     <row r="14">
       <c r="B14" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D14" s="6">
         <v>10</v>
@@ -3327,10 +3336,10 @@
     </row>
     <row r="15">
       <c r="B15" s="5" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D15" s="5">
         <v>11</v>
@@ -3338,10 +3347,10 @@
     </row>
     <row r="16">
       <c r="B16" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D16" s="6">
         <v>12</v>
@@ -3349,10 +3358,10 @@
     </row>
     <row r="17">
       <c r="B17" s="5" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D17" s="5">
         <v>13</v>
@@ -3360,10 +3369,10 @@
     </row>
     <row r="18">
       <c r="B18" s="6" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D18" s="6">
         <v>14</v>
@@ -3371,10 +3380,10 @@
     </row>
     <row r="19">
       <c r="B19" s="5" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D19" s="5">
         <v>15</v>
@@ -3382,10 +3391,10 @@
     </row>
     <row r="20">
       <c r="B20" s="6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D20" s="6">
         <v>16</v>
@@ -3393,10 +3402,10 @@
     </row>
     <row r="21">
       <c r="B21" s="5" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D21" s="5">
         <v>17</v>
@@ -3404,10 +3413,10 @@
     </row>
     <row r="22">
       <c r="B22" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D22" s="6">
         <v>18</v>
@@ -3421,7 +3430,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:BL31"/>
+  <dimension ref="A1:BM31"/>
   <sheetFormatPr defaultColWidth="8.43" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="49.21875" customWidth="1"/>
@@ -3472,15 +3481,15 @@
     <col min="59" max="60" width="23.4375" customWidth="1"/>
     <col min="61" max="61" width="18.75" customWidth="1"/>
     <col min="62" max="63" width="21.09375" customWidth="1"/>
-    <col min="64" max="64" width="22.265625" customWidth="1"/>
+    <col min="64" max="65" width="22.265625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
@@ -3544,6 +3553,7 @@
       <c r="BJ1" s="2"/>
       <c r="BK1" s="2"/>
       <c r="BL1" s="2"/>
+      <c r="BM1" s="2"/>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
@@ -3738,43 +3748,46 @@
       <c r="BL2" s="4" t="s">
         <v>122</v>
       </c>
+      <c r="BM2" s="4" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="G3" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="K3" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="H3" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="J3" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="K3" s="4" t="s">
-        <v>126</v>
-      </c>
       <c r="L3" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="M3" s="4"/>
       <c r="N3" s="4"/>
@@ -3791,7 +3804,7 @@
       <c r="Y3" s="4"/>
       <c r="Z3" s="4"/>
       <c r="AA3" s="4" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="AB3" s="4"/>
       <c r="AC3" s="4"/>
@@ -3830,43 +3843,44 @@
       <c r="BJ3" s="4"/>
       <c r="BK3" s="4"/>
       <c r="BL3" s="4"/>
+      <c r="BM3" s="4"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
         <v>10</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="L4" s="4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="M4" s="4"/>
       <c r="N4" s="4"/>
@@ -3883,7 +3897,7 @@
       <c r="Y4" s="4"/>
       <c r="Z4" s="4"/>
       <c r="AA4" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AB4" s="4"/>
       <c r="AC4" s="4"/>
@@ -3922,43 +3936,44 @@
       <c r="BJ4" s="4"/>
       <c r="BK4" s="4"/>
       <c r="BL4" s="4"/>
+      <c r="BM4" s="4"/>
     </row>
     <row r="5">
       <c r="B5" s="5" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C5" s="5">
         <v>0</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="K5" s="5">
         <v>1</v>
       </c>
       <c r="L5" s="5" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AA5" s="5" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AU5" s="5">
         <v>1</v>
@@ -3966,90 +3981,90 @@
     </row>
     <row r="6">
       <c r="B6" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C6" s="6">
         <v>1</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="K6" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L6" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AA6" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AT6" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AU6" s="6">
         <v>3</v>
       </c>
       <c r="AV6" s="6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="BJ6" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="7">
       <c r="B7" s="5" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C7" s="5">
         <v>0</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="K7" s="5">
         <v>1</v>
       </c>
       <c r="L7" s="5" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AA7" s="5" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AU7" s="5">
         <v>1</v>
@@ -4057,90 +4072,90 @@
     </row>
     <row r="8">
       <c r="B8" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C8" s="6">
         <v>1</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="K8" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L8" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AA8" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AT8" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AU8" s="6">
         <v>2</v>
       </c>
       <c r="AV8" s="6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="BJ8" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="9">
       <c r="B9" s="5" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C9" s="5">
         <v>0</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="K9" s="5">
         <v>1</v>
       </c>
       <c r="L9" s="5" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AA9" s="5" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AU9" s="5">
         <v>1</v>
@@ -4148,228 +4163,228 @@
     </row>
     <row r="10">
       <c r="B10" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C10" s="6">
         <v>1</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="K10" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L10" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AA10" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AT10" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AU10" s="6">
         <v>4</v>
       </c>
       <c r="AV10" s="6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="BJ10" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="11">
       <c r="B11" s="5" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C11" s="5">
         <v>0</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="K11" s="5">
         <v>1</v>
       </c>
       <c r="L11" s="5" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AA11" s="5" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AZ11" s="5" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="BB11" s="5" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C12" s="6">
         <v>0</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="K12" s="6">
         <v>1</v>
       </c>
       <c r="L12" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AA12" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="BB12" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="BJ12" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="5" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C13" s="5">
         <v>0</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="K13" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L13" s="5" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AA13" s="5" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="AT13" s="5" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AU13" s="5">
         <v>1</v>
       </c>
       <c r="AX13" s="5" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="BJ13" s="5" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C14" s="6">
         <v>1</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="K14" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L14" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AA14" s="6" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AD14" s="6">
         <v>0</v>
@@ -4377,257 +4392,257 @@
     </row>
     <row r="15">
       <c r="B15" s="5" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C15" s="5">
         <v>0</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J15" s="5" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="K15" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L15" s="5" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AA15" s="5" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="BB15" s="5" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="BJ15" s="5" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="6" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C16" s="6">
         <v>0</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J16" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="K16" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L16" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AA16" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="BB16" s="6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="BJ16" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="5" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C17" s="5">
         <v>1</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J17" s="5" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="K17" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L17" s="5" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AA17" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AH17" s="5">
         <v>-1</v>
       </c>
       <c r="BF17" s="5" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C18" s="6">
         <v>0</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J18" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="K18" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L18" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AA18" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AW18" s="6" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="5" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C19" s="5">
         <v>1</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I19" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J19" s="5" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="K19" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L19" s="5" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AA19" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AH19" s="5">
         <v>-1</v>
       </c>
       <c r="BF19" s="5" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C20" s="6">
         <v>0</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J20" s="6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="K20" s="6">
         <v>5</v>
       </c>
       <c r="L20" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AA20" s="6" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AU20" s="6">
         <v>5</v>
@@ -4635,40 +4650,40 @@
     </row>
     <row r="21">
       <c r="B21" s="5" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C21" s="5">
         <v>1</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I21" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J21" s="5" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="K21" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L21" s="5" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AA21" s="5" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AD21" s="5">
         <v>20</v>
@@ -4676,339 +4691,339 @@
     </row>
     <row r="22">
       <c r="B22" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C22" s="6">
         <v>0</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I22" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J22" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="K22" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L22" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AA22" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="BE22" s="6" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="23">
       <c r="B23" s="5" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C23" s="5">
         <v>1</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I23" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J23" s="5" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="K23" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L23" s="5" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AA23" s="5" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="BE23" s="5" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C24" s="6">
         <v>0</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I24" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J24" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="K24" s="6">
         <v>1</v>
       </c>
       <c r="L24" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AA24" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AZ24" s="6" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="BB24" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="25">
       <c r="B25" s="5" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C25" s="5">
         <v>0</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I25" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J25" s="5" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="K25" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L25" s="5" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AA25" s="5" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AW25" s="5" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="26">
       <c r="B26" s="6" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C26" s="6">
         <v>1</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I26" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J26" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="K26" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L26" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AA26" s="6" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="BE26" s="6" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="27">
       <c r="B27" s="5" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C27" s="5">
         <v>0</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H27" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I27" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J27" s="5" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="K27" s="5">
         <v>1</v>
       </c>
       <c r="L27" s="5" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AA27" s="5" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AZ27" s="5" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="BB27" s="5" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="28">
       <c r="B28" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C28" s="6">
         <v>0</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F28" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I28" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J28" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="K28" s="6">
         <v>1</v>
       </c>
       <c r="L28" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AA28" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AZ28" s="6" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="BB28" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="29">
       <c r="B29" s="5" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C29" s="5">
         <v>0</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H29" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I29" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J29" s="5" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="K29" s="5">
         <v>1</v>
       </c>
       <c r="L29" s="5" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AA29" s="5" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AT29" s="5" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AU29" s="5">
         <v>2</v>
@@ -5016,100 +5031,100 @@
     </row>
     <row r="30">
       <c r="B30" s="6" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C30" s="6">
         <v>0</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F30" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I30" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J30" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="K30" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L30" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AA30" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="AT30" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AU30" s="6">
         <v>1</v>
       </c>
       <c r="AX30" s="6" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="BJ30" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="31">
       <c r="B31" s="5" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C31" s="5">
         <v>0</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H31" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I31" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J31" s="5" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="K31" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L31" s="5" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AA31" s="5" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AR31" s="5" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AS31" s="5">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B2:BL31"/>
+  <autoFilter ref="B2:BM31"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>